--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.34170332618968</v>
+        <v>2.980526790505824</v>
       </c>
       <c r="D2" t="n">
-        <v>18.95952761054253</v>
+        <v>3.080923236713161</v>
       </c>
       <c r="E2" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F2" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.75924205662363</v>
+        <v>2.23587683420134</v>
       </c>
       <c r="D3" t="n">
-        <v>12.896562566739</v>
+        <v>2.095691417095087</v>
       </c>
       <c r="E3" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.96546179268205</v>
+        <v>5.681887541310833</v>
       </c>
       <c r="D4" t="n">
-        <v>34.41984984157034</v>
+        <v>5.59322559925518</v>
       </c>
       <c r="E4" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F4" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.25744520209136</v>
+        <v>5.404334845339847</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6132924882814</v>
+        <v>5.299660029345728</v>
       </c>
       <c r="E5" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F5" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.54575601398553</v>
+        <v>6.751185352272649</v>
       </c>
       <c r="D6" t="n">
-        <v>12.76604169035058</v>
+        <v>2.074481774681969</v>
       </c>
       <c r="E6" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F6" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.1990498515402</v>
+        <v>7.507345600875283</v>
       </c>
       <c r="D7" t="n">
-        <v>45.62729034156836</v>
+        <v>7.414434680504859</v>
       </c>
       <c r="E7" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F7" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.6159384399897</v>
+        <v>7.250089996498327</v>
       </c>
       <c r="D8" t="n">
-        <v>10.92016483392078</v>
+        <v>1.774526785512127</v>
       </c>
       <c r="E8" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F8" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.09424804356642</v>
+        <v>3.752815307079544</v>
       </c>
       <c r="D9" t="n">
-        <v>19.44964383027917</v>
+        <v>3.160567122420365</v>
       </c>
       <c r="E9" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F9" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.67840177177204</v>
+        <v>5.472740287912957</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88315096097014</v>
+        <v>5.506012031157648</v>
       </c>
       <c r="E10" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F10" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.80516696882969</v>
+        <v>2.405839632434825</v>
       </c>
       <c r="D11" t="n">
-        <v>15.10568421592338</v>
+        <v>2.454673685087549</v>
       </c>
       <c r="E11" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F11" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.96072598016838</v>
+        <v>5.356117971777363</v>
       </c>
       <c r="D12" t="n">
-        <v>32.38410784732728</v>
+        <v>5.262417525190683</v>
       </c>
       <c r="E12" t="n">
-        <v>11.03881600099554</v>
+        <v>1.793807600161776</v>
       </c>
       <c r="F12" t="n">
-        <v>11.12722741463686</v>
+        <v>1.808174454878491</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
